--- a/healthcare_surveys/016_neurological_serology_indications_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/016_neurological_serology_indications_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What are the patient's current symptoms?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe the patient's current symptoms.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Provide the patient's medical history.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe the patient's medical history.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Neurological Serology Testing</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Which type of serology test is ordered?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,46 +596,54 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>symptoms_page_2</t>
+          <t>frequency_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often is the serology test performed?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>history_page_2</t>
+          <t>time_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>History</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What is the patient's preferred time for the test?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,38 +655,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_2</t>
+          <t>results_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Neurological Serology Testing</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>What are the patient's serology test results?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_3</t>
+          <t>frequency_page_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How many times has the patient undergone a serology test?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,135 +704,159 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_4</t>
+          <t>age_group_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>What is the patient's age group?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_5</t>
+          <t>medical_specialty_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the patient's medical specialty?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_6</t>
+          <t>symptoms_page_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Which of the following symptoms have the patient experienced?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select all that apply.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_7</t>
+          <t>last_serology_test_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the date of the last serology test?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Format is MM/DD/YY.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_8</t>
+          <t>last_serology_test_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the time of the last serology test?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Format is HH -MM AM/PM.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_9</t>
+          <t>last_serology_test_note</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Additional information about the last serology test.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any additional information about the last serology test.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,43 +866,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_10</t>
+          <t>total_serology_tests</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>How many serology tests has the patient undergone?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_11</t>
+          <t>total_serology_tests_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>What is the total number of serology tests undergone?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -860,230 +920,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_12</t>
+          <t>total_serology_tests_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Total Serology Tests 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select one option.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_13</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_16</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>neurological_serology_testing_page_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Serology Test</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +955,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,160 +1034,160 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_2_choices</t>
+          <t>frequency_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>blood_tests</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Blood tests</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_2_choices</t>
+          <t>frequency_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>imaging_studies</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Imaging studies</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_2_choices</t>
+          <t>frequency_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>physical_exam</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Physical exam</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_8_choices</t>
+          <t>time_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_8_choices</t>
+          <t>time_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_9_choices</t>
+          <t>time_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_9_choices</t>
+          <t>results_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_16_choices</t>
+          <t>results_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_16_choices</t>
+          <t>results_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inconclusive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_17_choices</t>
+          <t>frequency_page_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1204,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>neurological_serology_testing_page_17_choices</t>
+          <t>frequency_page_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1358,6 +1215,465 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>frequency_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>age_group_page_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0-10_years</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0-10 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>age_group_page_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>11-20_years</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11-20 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>age_group_page_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21-30_years</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>21-30 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>medical_specialty_page_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>neurologist</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Neurologist</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>medical_specialty_page_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>primary_care_physician</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Primary care physician</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>medical_specialty_page_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>specialist</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Specialist</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dizziness</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dizziness</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>numbness</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Numbness</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>tingling_sensation_in_hands_and_feet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tingling sensation in hands and feet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fatigue</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fatigue</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>weakness</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Weakness</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>confusion_or_disorientation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Confusion or disorientation</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>vision_changes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vision changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>hearing_loss</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hearing loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>speech_or_language_changes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Speech or language changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>symptoms_page_2_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>memory_loss</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Memory loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>total_serology_tests_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>total_serology_tests_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>total_serology_tests_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>total_serology_tests_2_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_serology_tests_2_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>6-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>total_serology_tests_2_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>11-15</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>total_serology_tests_3_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>total_serology_tests_3_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>total_serology_tests_3_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>21_or_more</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21 or more</t>
         </is>
       </c>
     </row>
